--- a/SendSignal_Bot/Data.xlsx
+++ b/SendSignal_Bot/Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/42000ae913e9c605/Máy tính/TelegramTool/SendSignal_Bot/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="11_8414EC884DAE0A01AFB5B99D4F7858E5908E52DB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58A00912-06D5-48B8-9985-941732AB7B59}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="11_8414EC884DAE0A01AFB5B99D4F7858E5908E52DB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6A2B052-BA37-4127-8C00-956E245CE4DD}"/>
   <bookViews>
-    <workbookView xWindow="690" yWindow="5535" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7350" yWindow="5385" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Mã_API</t>
   </si>
@@ -49,7 +49,10 @@
     <t>78a876eeffc794a5f65af8f802e9db67</t>
   </si>
   <si>
-    <t>08:59</t>
+    <t>-1003814615658</t>
+  </si>
+  <si>
+    <t>08:00</t>
   </si>
 </sst>
 </file>
@@ -244,9 +247,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -263,6 +263,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -611,26 +614,26 @@
       <c r="B2" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="16">
-        <v>-5156893190</v>
-      </c>
-      <c r="D2" s="17">
+      <c r="C2" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="16">
         <v>80</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="19" t="s">
-        <v>9</v>
+      <c r="F2" s="18" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
+      <c r="A3" s="19"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
     </row>
     <row r="4" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>

--- a/SendSignal_Bot/Data.xlsx
+++ b/SendSignal_Bot/Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/42000ae913e9c605/Máy tính/TelegramTool/SendSignal_Bot/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="11_8414EC884DAE0A01AFB5B99D4F7858E5908E52DB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6A2B052-BA37-4127-8C00-956E245CE4DD}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="11_8414EC884DAE0A01AFB5B99D4F7858E5908E52DB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17726B5A-40F9-4D24-BA55-C7277934302B}"/>
   <bookViews>
     <workbookView xWindow="7350" yWindow="5385" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
     <t>-1003814615658</t>
   </si>
   <si>
-    <t>08:00</t>
+    <t>07:00</t>
   </si>
 </sst>
 </file>

--- a/SendSignal_Bot/Data.xlsx
+++ b/SendSignal_Bot/Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/42000ae913e9c605/Máy tính/TelegramTool/SendSignal_Bot/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="11_8414EC884DAE0A01AFB5B99D4F7858E5908E52DB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17726B5A-40F9-4D24-BA55-C7277934302B}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_988320B796F2D27AEAE68DA7E5523E8270FFCB01" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{181A7A27-9E0B-421D-9FC2-F4A88C71EA30}"/>
   <bookViews>
-    <workbookView xWindow="7350" yWindow="5385" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6210" yWindow="5535" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Mã_API</t>
   </si>
@@ -34,32 +34,38 @@
     <t>Pord</t>
   </si>
   <si>
+    <t>Token</t>
+  </si>
+  <si>
+    <t>Giờ_Tổng_Kết</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Web_URL </t>
+  </si>
+  <si>
+    <t>30711256</t>
+  </si>
+  <si>
+    <t>78a876eeffc794a5f65af8f802e9db67</t>
+  </si>
+  <si>
+    <t>-1003814615658</t>
+  </si>
+  <si>
     <t>xK9mQw2pLr7nTv4j</t>
   </si>
   <si>
-    <t>Token</t>
-  </si>
-  <si>
-    <t>Giờ_Tổng_Kết</t>
-  </si>
-  <si>
-    <t>30711256</t>
-  </si>
-  <si>
-    <t>78a876eeffc794a5f65af8f802e9db67</t>
-  </si>
-  <si>
-    <t>-1003814615658</t>
-  </si>
-  <si>
     <t>07:00</t>
+  </si>
+  <si>
+    <t>http://217.15.161.96/trading/tv-webhook/richfound2024/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -105,6 +111,14 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -114,7 +128,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -198,13 +212,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="24">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="28">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -213,10 +241,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -238,10 +266,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -251,7 +279,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -264,11 +291,23 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -576,7 +615,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.85546875" style="4" bestFit="1" customWidth="1"/>
@@ -585,9 +624,10 @@
     <col min="4" max="4" width="15.7109375" style="5" customWidth="1"/>
     <col min="5" max="5" width="29.28515625" customWidth="1"/>
     <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -601,337 +641,384 @@
         <v>3</v>
       </c>
       <c r="E1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="G1" s="26" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="22" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="16">
         <v>80</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="18" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="19"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-    </row>
-    <row r="4" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F2" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="27" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="18"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="7"/>
+    </row>
+    <row r="4" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="3"/>
       <c r="C4" s="2"/>
       <c r="D4" s="6"/>
       <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-    </row>
-    <row r="5" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F4" s="25"/>
+      <c r="G4" s="7"/>
+    </row>
+    <row r="5" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="3"/>
       <c r="C5" s="2"/>
       <c r="D5" s="6"/>
       <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-    </row>
-    <row r="6" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F5" s="25"/>
+      <c r="G5" s="7"/>
+    </row>
+    <row r="6" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="3"/>
       <c r="C6" s="2"/>
       <c r="D6" s="6"/>
       <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F6" s="25"/>
+      <c r="G6" s="7"/>
+    </row>
+    <row r="7" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="3"/>
       <c r="C7" s="2"/>
       <c r="D7" s="6"/>
       <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-    </row>
-    <row r="8" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F7" s="25"/>
+      <c r="G7" s="7"/>
+    </row>
+    <row r="8" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="3"/>
       <c r="C8" s="2"/>
       <c r="D8" s="6"/>
       <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-    </row>
-    <row r="9" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F8" s="25"/>
+      <c r="G8" s="7"/>
+    </row>
+    <row r="9" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="3"/>
       <c r="C9" s="2"/>
       <c r="D9" s="6"/>
       <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-    </row>
-    <row r="10" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F9" s="25"/>
+      <c r="G9" s="7"/>
+    </row>
+    <row r="10" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" s="2"/>
       <c r="D10" s="6"/>
       <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-    </row>
-    <row r="11" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F10" s="25"/>
+      <c r="G10" s="7"/>
+    </row>
+    <row r="11" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="3"/>
       <c r="C11" s="2"/>
       <c r="D11" s="6"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-    </row>
-    <row r="12" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F11" s="25"/>
+      <c r="G11" s="7"/>
+    </row>
+    <row r="12" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="3"/>
       <c r="C12" s="2"/>
       <c r="D12" s="6"/>
       <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-    </row>
-    <row r="13" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F12" s="25"/>
+      <c r="G12" s="7"/>
+    </row>
+    <row r="13" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="3"/>
       <c r="C13" s="2"/>
       <c r="D13" s="6"/>
       <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-    </row>
-    <row r="14" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F13" s="25"/>
+      <c r="G13" s="7"/>
+    </row>
+    <row r="14" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="3"/>
       <c r="C14" s="2"/>
       <c r="D14" s="6"/>
       <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-    </row>
-    <row r="15" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F14" s="25"/>
+      <c r="G14" s="7"/>
+    </row>
+    <row r="15" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="3"/>
       <c r="C15" s="2"/>
       <c r="D15" s="6"/>
       <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="16" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F15" s="25"/>
+      <c r="G15" s="7"/>
+    </row>
+    <row r="16" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="3"/>
       <c r="C16" s="2"/>
       <c r="D16" s="6"/>
       <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-    </row>
-    <row r="17" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F16" s="25"/>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="3"/>
       <c r="C17" s="2"/>
       <c r="D17" s="6"/>
       <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-    </row>
-    <row r="18" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F17" s="25"/>
+      <c r="G17" s="7"/>
+    </row>
+    <row r="18" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="3"/>
       <c r="C18" s="2"/>
       <c r="D18" s="6"/>
       <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-    </row>
-    <row r="19" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F18" s="25"/>
+      <c r="G18" s="7"/>
+    </row>
+    <row r="19" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="3"/>
       <c r="C19" s="2"/>
       <c r="D19" s="6"/>
       <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-    </row>
-    <row r="20" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F19" s="25"/>
+      <c r="G19" s="7"/>
+    </row>
+    <row r="20" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="3"/>
       <c r="C20" s="2"/>
       <c r="D20" s="6"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-    </row>
-    <row r="21" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F20" s="25"/>
+      <c r="G20" s="7"/>
+    </row>
+    <row r="21" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="3"/>
       <c r="C21" s="2"/>
       <c r="D21" s="6"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-    </row>
-    <row r="22" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F21" s="25"/>
+      <c r="G21" s="7"/>
+    </row>
+    <row r="22" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="3"/>
       <c r="C22" s="2"/>
       <c r="D22" s="6"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-    </row>
-    <row r="23" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F22" s="25"/>
+      <c r="G22" s="7"/>
+    </row>
+    <row r="23" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="3"/>
       <c r="C23" s="2"/>
       <c r="D23" s="6"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-    </row>
-    <row r="24" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F23" s="25"/>
+      <c r="G23" s="7"/>
+    </row>
+    <row r="24" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="3"/>
       <c r="C24" s="2"/>
       <c r="D24" s="6"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-    </row>
-    <row r="25" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F24" s="25"/>
+      <c r="G24" s="7"/>
+    </row>
+    <row r="25" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="3"/>
       <c r="C25" s="2"/>
       <c r="D25" s="6"/>
       <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-    </row>
-    <row r="26" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F25" s="25"/>
+      <c r="G25" s="7"/>
+    </row>
+    <row r="26" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="3"/>
       <c r="C26" s="2"/>
       <c r="D26" s="6"/>
       <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-    </row>
-    <row r="27" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F26" s="25"/>
+      <c r="G26" s="7"/>
+    </row>
+    <row r="27" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="3"/>
       <c r="C27" s="2"/>
       <c r="D27" s="6"/>
       <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-    </row>
-    <row r="28" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F27" s="25"/>
+      <c r="G27" s="7"/>
+    </row>
+    <row r="28" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="3"/>
       <c r="C28" s="2"/>
       <c r="D28" s="6"/>
       <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-    </row>
-    <row r="29" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F28" s="25"/>
+      <c r="G28" s="7"/>
+    </row>
+    <row r="29" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="3"/>
       <c r="C29" s="2"/>
       <c r="D29" s="6"/>
       <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-    </row>
-    <row r="30" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F29" s="25"/>
+      <c r="G29" s="7"/>
+    </row>
+    <row r="30" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="3"/>
       <c r="C30" s="2"/>
       <c r="D30" s="6"/>
       <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-    </row>
-    <row r="31" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F30" s="25"/>
+      <c r="G30" s="7"/>
+    </row>
+    <row r="31" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="3"/>
       <c r="C31" s="2"/>
       <c r="D31" s="6"/>
       <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-    </row>
-    <row r="32" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F31" s="25"/>
+      <c r="G31" s="7"/>
+    </row>
+    <row r="32" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="3"/>
       <c r="C32" s="2"/>
       <c r="D32" s="6"/>
       <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-    </row>
-    <row r="33" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F32" s="25"/>
+      <c r="G32" s="7"/>
+    </row>
+    <row r="33" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="3"/>
       <c r="C33" s="2"/>
       <c r="D33" s="6"/>
       <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-    </row>
-    <row r="34" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F33" s="25"/>
+      <c r="G33" s="7"/>
+    </row>
+    <row r="34" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="3"/>
       <c r="C34" s="2"/>
       <c r="D34" s="6"/>
       <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-    </row>
-    <row r="35" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F34" s="25"/>
+      <c r="G34" s="7"/>
+    </row>
+    <row r="35" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="3"/>
       <c r="C35" s="2"/>
       <c r="D35" s="6"/>
       <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-    </row>
-    <row r="36" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F35" s="25"/>
+      <c r="G35" s="7"/>
+    </row>
+    <row r="36" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="3"/>
       <c r="C36" s="2"/>
       <c r="D36" s="6"/>
       <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-    </row>
-    <row r="37" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F36" s="25"/>
+      <c r="G36" s="7"/>
+    </row>
+    <row r="37" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="3"/>
       <c r="C37" s="2"/>
       <c r="D37" s="6"/>
       <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-    </row>
-    <row r="38" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F37" s="25"/>
+      <c r="G37" s="7"/>
+    </row>
+    <row r="38" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="3"/>
       <c r="C38" s="2"/>
       <c r="D38" s="6"/>
       <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-    </row>
-    <row r="39" spans="1:6" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F38" s="25"/>
+      <c r="G38" s="7"/>
+    </row>
+    <row r="39" spans="1:7" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="3"/>
       <c r="C39" s="2"/>
       <c r="D39" s="6"/>
       <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-    </row>
-    <row r="40" spans="1:6" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F39" s="25"/>
+      <c r="G39" s="7"/>
+    </row>
+    <row r="40" spans="1:7" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="3"/>
       <c r="C40" s="2"/>
       <c r="D40" s="6"/>
       <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="7"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/SendSignal_Bot/Data.xlsx
+++ b/SendSignal_Bot/Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/42000ae913e9c605/Máy tính/TelegramTool/SendSignal_Bot/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_988320B796F2D27AEAE68DA7E5523E8270FFCB01" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{181A7A27-9E0B-421D-9FC2-F4A88C71EA30}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_988320B796F2D27AEAE68DA7E5523E8270FFCB01" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2AF7C9A-69F3-42EB-B4D9-33A6DDC4726E}"/>
   <bookViews>
     <workbookView xWindow="6210" yWindow="5535" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,9 +40,6 @@
     <t>Giờ_Tổng_Kết</t>
   </si>
   <si>
-    <t xml:space="preserve">Web_URL </t>
-  </si>
-  <si>
     <t>30711256</t>
   </si>
   <si>
@@ -58,7 +55,10 @@
     <t>07:00</t>
   </si>
   <si>
-    <t>http://217.15.161.96/trading/tv-webhook/richfound2024/</t>
+    <t>Web_URL</t>
+  </si>
+  <si>
+    <t>https://richaitrading.com/trading/tv-webhook/richfound2024/</t>
   </si>
 </sst>
 </file>
@@ -304,7 +304,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -624,7 +624,7 @@
     <col min="4" max="4" width="15.7109375" style="5" customWidth="1"/>
     <col min="5" max="5" width="29.28515625" customWidth="1"/>
     <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.28515625" customWidth="1"/>
+    <col min="7" max="7" width="58.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -647,27 +647,27 @@
         <v>5</v>
       </c>
       <c r="G1" s="26" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="C2" s="22" t="s">
         <v>8</v>
-      </c>
-      <c r="C2" s="22" t="s">
-        <v>9</v>
       </c>
       <c r="D2" s="16">
         <v>80</v>
       </c>
       <c r="E2" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="23" t="s">
         <v>10</v>
-      </c>
-      <c r="F2" s="23" t="s">
-        <v>11</v>
       </c>
       <c r="G2" s="27" t="s">
         <v>12</v>

--- a/SendSignal_Bot/Data.xlsx
+++ b/SendSignal_Bot/Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/42000ae913e9c605/Máy tính/TelegramTool/SendSignal_Bot/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_988320B796F2D27AEAE68DA7E5523E8270FFCB01" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2AF7C9A-69F3-42EB-B4D9-33A6DDC4726E}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_988320B796F2D27AEAE68DA7E5523E8270FFCB01" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41EF8DA6-E05C-45CF-A6C3-F2F6CBB0329B}"/>
   <bookViews>
     <workbookView xWindow="6210" yWindow="5535" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
     <t>Web_URL</t>
   </si>
   <si>
-    <t>https://richaitrading.com/trading/tv-webhook/richfound2024/</t>
+    <t>https://richaitrading.com/trading/tv-webhook/richfound2024/rich-scalping/</t>
   </si>
 </sst>
 </file>
@@ -624,7 +624,7 @@
     <col min="4" max="4" width="15.7109375" style="5" customWidth="1"/>
     <col min="5" max="5" width="29.28515625" customWidth="1"/>
     <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="58.5703125" customWidth="1"/>
+    <col min="7" max="7" width="73.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
